--- a/site/Dayforce-iCIMS-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-iCIMS-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,12 +649,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KTKARPGBWF117DXKWG3BEESW</t>
+          <t>h_01KTKJAR71QP838EN4MAJ4WRP8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKARPGBWF117DXKWG3BEESW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR71QP838EN4MAJ4WRP8</t>
         </is>
       </c>
     </row>
@@ -671,12 +671,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KTKARPGBQ2Z3F5Z6WGYD4ZCM</t>
+          <t>h_01KTKJAR718P91VZ83VFSAXBZ4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKARPGBQ2Z3F5Z6WGYD4ZCM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR718P91VZ83VFSAXBZ4</t>
         </is>
       </c>
     </row>
@@ -693,12 +693,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KTKARPGBFZHC74121F0NMY2X</t>
+          <t>h_01KTKJAR71QNZM4S141TZQBKGB</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKARPGBFZHC74121F0NMY2X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR71QNZM4S141TZQBKGB</t>
         </is>
       </c>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KTKARPGBHTZR5JZC6YZ01YTP</t>
+          <t>h_01KTKJAR71KGJWMVZ6ZVARDESH</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKARPGBHTZR5JZC6YZ01YTP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR71KGJWMVZ6ZVARDESH</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KTKARPGBXDT2B73FHTZZF53X</t>
+          <t>h_01KTKJAR71Z4B1S88GHXC6S8WW</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKARPGBXDT2B73FHTZZF53X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR71Z4B1S88GHXC6S8WW</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KTKARPGBSJAWY7NF91GD81AZ</t>
+          <t>h_01KTKJAR71M849SHH760HKYVG2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKARPGBSJAWY7NF91GD81AZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR71M849SHH760HKYVG2</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,98 +825,208 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KTK4883GSGGVG49VRBTGVTPV</t>
+          <t>h_01KTKHFWYE9QSY246CDNW9K5JH</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTK4883GSGGVG49VRBTGVTPV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKHFWYE9QSY246CDNW9K5JH</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>PII Attributes</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KTKJAR72N5EM93JG21VT5NKM</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR72N5EM93JG21VT5NKM</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KTKJAR727BM044PZD1WDE552</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR727BM044PZD1WDE552</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Advance Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KTKJAR729EESN96B1T31MBDJ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR729EESN96B1T31MBDJ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Rollout Configurations</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KTKJAR72CGWCVR2P05BYFJRB</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR72CGWCVR2P05BYFJRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KTK4883GSGGVG49VRBTGVTPV</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTK4883GSGGVG49VRBTGVTPV</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/Dayforce-iCIMS-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-iCIMS-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -925,29 +925,29 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Safeguard Limits</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KTK4883GSGGVG49VRBTGVTPV</t>
+          <t>h_01KTNEEDT6DTTWNKKQVNANKB11</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTK4883GSGGVG49VRBTGVTPV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTNEEDT6DTTWNKKQVNANKB11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,41 +957,41 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KTK4883GSGGVG49VRBTGVTPV</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTK4883GSGGVG49VRBTGVTPV</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,32 +1001,54 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/Dayforce-iCIMS-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-iCIMS-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,73 +573,73 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>iCIMS</t>
+          <t>Integration Features</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01KTK44D2WWSVCZZAD6T2QY62B</t>
+          <t>h_01KRZRTP24GG27V8XGHD14MYMG</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTK44D2WWSVCZZAD6T2QY62B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KRZRTP24GG27V8XGHD14MYMG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>iCIMS Settings</t>
+          <t>iCIMS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KTK5RKGBPHMNC6S9RSX4AZ49</t>
+          <t>h_01KTK44D2WWSVCZZAD6T2QY62B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTK5RKGBPHMNC6S9RSX4AZ49</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTK44D2WWSVCZZAD6T2QY62B</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>iCIMS Source Application</t>
+          <t>iCIMS Settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KTK85C2M3MGGD64J7N9JTC5D</t>
+          <t>h_01KTK5RKGBPHMNC6S9RSX4AZ49</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTK85C2M3MGGD64J7N9JTC5D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTK5RKGBPHMNC6S9RSX4AZ49</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iCIMS Configuration</t>
+          <t>iCIMS Source Application</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,107 +649,107 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KTKJAR71QP838EN4MAJ4WRP8</t>
+          <t>h_01KTK85C2M3MGGD64J7N9JTC5D</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR71QP838EN4MAJ4WRP8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTK85C2M3MGGD64J7N9JTC5D</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Candidate Management</t>
+          <t>iCIMS Configuration</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KTKJAR718P91VZ83VFSAXBZ4</t>
+          <t>h_01KTKJAR71QP838EN4MAJ4WRP8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR718P91VZ83VFSAXBZ4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR71QP838EN4MAJ4WRP8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Candidate Configuration</t>
+          <t>Candidate Management</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KTKJAR71QNZM4S141TZQBKGB</t>
+          <t>h_01KTKJAR718P91VZ83VFSAXBZ4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR71QNZM4S141TZQBKGB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR718P91VZ83VFSAXBZ4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Candidate Configuration</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KTK44VGGS80HDQ36ZTJRZB9K</t>
+          <t>h_01KTKJAR71QNZM4S141TZQBKGB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTK44VGGS80HDQ36ZTJRZB9K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR71QNZM4S141TZQBKGB</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dayforce Settings</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KTKJAR71KGJWMVZ6ZVARDESH</t>
+          <t>h_01KTK44VGGS80HDQ36ZTJRZB9K</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR71KGJWMVZ6ZVARDESH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTK44VGGS80HDQ36ZTJRZB9K</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Employee Management</t>
+          <t>Dayforce Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,41 +759,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KTKJAR71Z4B1S88GHXC6S8WW</t>
+          <t>h_01KTKJAR71KGJWMVZ6ZVARDESH</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR71Z4B1S88GHXC6S8WW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR71KGJWMVZ6ZVARDESH</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Employee Management</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KTKJAR71M849SHH760HKYVG2</t>
+          <t>h_01KTKJAR71Z4B1S88GHXC6S8WW</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR71M849SHH760HKYVG2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR71Z4B1S88GHXC6S8WW</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>iCIMS Candidate to Dayforce Employee</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,129 +803,129 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KTK8EH51A55GPNCVQHEB9CXC</t>
+          <t>h_01KTKJAR71M849SHH760HKYVG2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTK8EH51A55GPNCVQHEB9CXC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR71M849SHH760HKYVG2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>iCIMS Candidate to Dayforce Employee</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KTKHFWYE9QSY246CDNW9K5JH</t>
+          <t>h_01KTK8EH51A55GPNCVQHEB9CXC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKHFWYE9QSY246CDNW9K5JH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTK8EH51A55GPNCVQHEB9CXC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PII Attributes</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KTKJAR72N5EM93JG21VT5NKM</t>
+          <t>h_01KTKHFWYE9QSY246CDNW9K5JH</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR72N5EM93JG21VT5NKM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKHFWYE9QSY246CDNW9K5JH</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>PII Attributes</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KTKJAR727BM044PZD1WDE552</t>
+          <t>h_01KTKJAR72N5EM93JG21VT5NKM</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR727BM044PZD1WDE552</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR72N5EM93JG21VT5NKM</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Advance Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KTKJAR729EESN96B1T31MBDJ</t>
+          <t>h_01KTKJAR727BM044PZD1WDE552</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR729EESN96B1T31MBDJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR727BM044PZD1WDE552</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rollout Configurations</t>
+          <t>Advance Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KTKJAR72CGWCVR2P05BYFJRB</t>
+          <t>h_01KTKJAR729EESN96B1T31MBDJ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR72CGWCVR2P05BYFJRB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR729EESN96B1T31MBDJ</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Safeguard Limits</t>
+          <t>Rollout Configurations</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,41 +935,41 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KTNEEDT6DTTWNKKQVNANKB11</t>
+          <t>h_01KTKJAR72CGWCVR2P05BYFJRB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTNEEDT6DTTWNKKQVNANKB11</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTKJAR72CGWCVR2P05BYFJRB</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Safeguard Limits</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KTK4883GSGGVG49VRBTGVTPV</t>
+          <t>h_01KTNTXZ4DRNCSMJW099KKJPSY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTK4883GSGGVG49VRBTGVTPV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTNTXZ4DRNCSMJW099KKJPSY</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,76 +979,230 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KTNTXZ4D3PD968YG2V7MPFQP</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTNTXZ4D3PD968YG2V7MPFQP</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KTNTXZ4DK0RBF7JX2ASAEPZM</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTNTXZ4DK0RBF7JX2ASAEPZM</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Insights Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KTNTXZ4D3SATH4HWN7VD7K8V</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTNTXZ4D3SATH4HWN7VD7K8V</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KTNTXZ4DCF0RPRA3TJYC0W01</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTNTXZ4DCF0RPRA3TJYC0W01</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Logging Settings</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KTNTXZ4DXNM116W2JMVYT7G1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTNTXZ4DXNM116W2JMVYT7G1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Notification</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KTNTXZ4DFS890NA8Y1V68GMQ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTNTXZ4DFS890NA8Y1V68GMQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01KTK4883GSGGVG49VRBTGVTPV</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTK4883GSGGVG49VRBTGVTPV</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/Dayforce-iCIMS-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-iCIMS-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iCIMS Source Application</t>
+          <t>Source Application</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>iCIMS Configuration</t>
+          <t>Source Application Configuration</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KTNTXZ4DRNCSMJW099KKJPSY</t>
+          <t>h_01KTP5340JMXBNF9HYWA8Z8R13</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTNTXZ4DRNCSMJW099KKJPSY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP5340JMXBNF9HYWA8Z8R13</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KTNTXZ4D3PD968YG2V7MPFQP</t>
+          <t>h_01KTP5340JJEFVJ2TN7YFDCHVG</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTNTXZ4D3PD968YG2V7MPFQP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP5340JJEFVJ2TN7YFDCHVG</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KTNTXZ4DK0RBF7JX2ASAEPZM</t>
+          <t>h_01KTP5340J9WX1ZCXMQFBB7XQJ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTNTXZ4DK0RBF7JX2ASAEPZM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP5340J9WX1ZCXMQFBB7XQJ</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KTNTXZ4D3SATH4HWN7VD7K8V</t>
+          <t>h_01KTP5340JVXY5T34NZMV2C4SF</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTNTXZ4D3SATH4HWN7VD7K8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP5340JVXY5T34NZMV2C4SF</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KTNTXZ4DCF0RPRA3TJYC0W01</t>
+          <t>h_01KTP5340JEM98BXV8DZ6TH812</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTNTXZ4DCF0RPRA3TJYC0W01</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP5340JEM98BXV8DZ6TH812</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KTNTXZ4DXNM116W2JMVYT7G1</t>
+          <t>h_01KTP5340JJQV63KQV3EZYV17R</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTNTXZ4DXNM116W2JMVYT7G1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP5340JJQV63KQV3EZYV17R</t>
         </is>
       </c>
     </row>
@@ -1089,19 +1089,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KTNTXZ4DFS890NA8Y1V68GMQ</t>
+          <t>h_01KTP5340J6NK293D3N09T4NF7</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTNTXZ4DFS890NA8Y1V68GMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP5340J6NK293D3N09T4NF7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,41 +1111,41 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KTK4883GSGGVG49VRBTGVTPV</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTK4883GSGGVG49VRBTGVTPV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,19 +1155,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1177,32 +1177,10 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Update the Integration to the Latest Version</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/Dayforce-iCIMS-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-iCIMS-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,7 +903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Advance Settings</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -925,7 +925,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rollout Configurations</t>
+          <t>Safeguard Limits</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -947,73 +947,73 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Safeguard Limits</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KTP5340JMXBNF9HYWA8Z8R13</t>
+          <t>h_01KTP69R262HW1B3AJRPESSBDZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP5340JMXBNF9HYWA8Z8R13</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP69R262HW1B3AJRPESSBDZ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KTP5340JJEFVJ2TN7YFDCHVG</t>
+          <t>h_01KTP69R26MC7K6TYPXAS3EP2G</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP5340JJEFVJ2TN7YFDCHVG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP69R26MC7K6TYPXAS3EP2G</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Insights Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KTP5340J9WX1ZCXMQFBB7XQJ</t>
+          <t>h_01KTP69R26KEK9SZSZR3178FM0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP5340J9WX1ZCXMQFBB7XQJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP69R26KEK9SZSZR3178FM0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Insights Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KTP5340JVXY5T34NZMV2C4SF</t>
+          <t>h_01KTP69R268KP360YWM1A7SS97</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP5340JVXY5T34NZMV2C4SF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP69R268KP360YWM1A7SS97</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,85 +1045,85 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KTP5340JEM98BXV8DZ6TH812</t>
+          <t>h_01KTP69R26Z6VCQ182Y9H4QCQ1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP5340JEM98BXV8DZ6TH812</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP69R26Z6VCQ182Y9H4QCQ1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KTP5340JJQV63KQV3EZYV17R</t>
+          <t>h_01KTP69R2788KRGJPZGJFT3JAK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP5340JJQV63KQV3EZYV17R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP69R2788KRGJPZGJFT3JAK</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KTP5340J6NK293D3N09T4NF7</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KTP5340J6NK293D3N09T4NF7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,19 +1133,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,32 +1155,10 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Update the Integration to the Latest Version</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
